--- a/reports/history/android/build-20/Excel/Failed_Test_Cases.xlsx
+++ b/reports/history/android/build-20/Excel/Failed_Test_Cases.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,15 +37,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -62,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="002A4D7C"/>
         <bgColor rgb="002A4D7C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
-        <bgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,20 +84,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,17 +457,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="4188" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -537,115 +517,6 @@
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Failure Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>TC_GEN_006</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>test_disease_scanner_page_load</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>63.02</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 08:29:08</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>auth_driver = &lt;appium.webdriver.webdriver.WebDriver (session="caec251d-484a-4d98-9a09-a0a6753be343")&gt;
-    def test_disease_scanner_page_load(auth_driver):
-        """Verify that the Disease Scanner interface opens successfully."""
-        home_page = HomePage(auth_driver)
-        # Scroll down to reveal the quick actions grid
-        home_page.swipe(720, 1600, 720, 800, 300)
-        # Click Scan Disease quick action card
-&gt;       home_page.click(home_page.SCAN_DISEASE_TILE)
-tests/mobile_e2e/test_suites/test_features.py:66: 
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-tests/mobile_e2e/pages/base_page.py:26: in click
-    element = self.wait_for_element(locator)
-              ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-tests/mobile_e2e/pages/base_page.py:22: in wait_for_element
-    raise e
-tests/mobile_e2e/pages/base_page.py:17: in wait_for_element
-    return WebDriverWait(self.driver, self.timeout).until(
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-self = &lt;selenium.webdriver.support.wait.WebDriverWait (session="caec251d-484a-4d98-9a09-a0a6753be343")&gt;
-method = &lt;function visibility_of_element_located.&lt;locals&gt;._predicate at 0x7fd013d99d00&gt;
-message = ''
-    def until(self, method: Callable[[D], Literal[False] | T], message: str = "") -&gt; T:
-        """Wait until the method returns a value that is not False.
-        Calls the method provided with the driver as an argument until the
-        return value does not evaluate to ``False``.
-        Args:
-            method: A callable object that takes a WebDriver instance as an
-                argument.
-            message: Optional message for TimeoutException.
-        Returns:
-            The result of the last call to `method`.
-        Raises:
-            TimeoutException: If 'method' does not return a truthy value within
-                the WebDriverWait object's timeout.
-        Example:
-            &gt;&gt;&gt; from selenium.webdriver.common.by import By
-            &gt;&gt;&gt; from selenium.webdriver.support.ui import WebDriverWait
-            &gt;&gt;&gt; from selenium.webdriver.support import expected_conditions as EC
-            &gt;&gt;&gt;
-            &gt;&gt;&gt; # Wait until an element is visible on the page
-            &gt;&gt;&gt; wait = WebDriverWait(driver, 10)
-            &gt;&gt;&gt; element = wait.until(EC.visibility_of_element_located((By.ID, "exampleId")))
-            &gt;&gt;&gt; print(element.text)
-        """
-        screen = None
-        stacktrace = None
-        end_time = time.monotonic() + self._timeout
-        while True:
-            try:
-                value = method(self._driver)
-                if value:
-                    return value
-            except self._ignored_exceptions as exc:
-                screen = getattr(exc, "screen", None)
-                stacktrace = getattr(exc, "stacktrace", None)
-            if time.monotonic() &gt; end_time:
-                break
-            time.sleep(self._poll)
-&gt;       raise TimeoutException(message, screen, stacktrace)
-E       selenium.common.exceptions.TimeoutException: Message: 
-E       Stacktrace:
-E       NoSuchElementError: An element could not be located on the page using the given search parameters.
-E           at AndroidUiautomator2Driver.findElOrEls (/home/runner/.appium/node_modules/appium-uiautomator2-driver/node_modules/appium-android-driver/build/lib/commands/find.js:62:15)
-E           at process.processTicksAndRejections (node:internal/process/task_queues:95:5)
-E           at async AndroidUiautomator2Driver.findElOrElsWithProcessing (/opt/hostedtoolcache/node/20.20.2/x64/lib/node_modules/appium/node_modules/@appium/base-driver/build/lib/basedriver/commands/find.js:12:16)
-E           at async AndroidUiautomator2Driver.findElement (/opt/hostedtoolcache/node/20.20.2/x64/lib/node_modules/appium/node_modules/@appium/base-driver/build/lib/basedriver/commands/find.js:28:16)
-E           at async runCommandPromise (/opt/hostedtoolcache/node/20.20.2/x64/lib/node_modules/appium/node_modules/@appium/base-driver/build/lib/basedriver/driver.js:119:24)
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/support/wait.py:121: TimeoutException</t>
         </is>
       </c>
     </row>
